--- a/ExportExcel/Search Tests.xlsx
+++ b/ExportExcel/Search Tests.xlsx
@@ -41,31 +41,31 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>1527 ms</t>
-  </si>
-  <si>
-    <t>1720 ms</t>
-  </si>
-  <si>
-    <t>1240 ms</t>
-  </si>
-  <si>
-    <t>2132 ms</t>
-  </si>
-  <si>
-    <t>1770 ms</t>
+    <t>1520 ms</t>
+  </si>
+  <si>
+    <t>4723 ms</t>
+  </si>
+  <si>
+    <t>3499 ms</t>
+  </si>
+  <si>
+    <t>1364 ms</t>
+  </si>
+  <si>
+    <t>1266 ms</t>
   </si>
   <si>
     <t>FAILED</t>
   </si>
   <si>
-    <t>1566 ms</t>
+    <t>1405 ms</t>
   </si>
   <si>
     <t>First product should not be displayed for search:    Quần Jean   expected [false] but found [true]</t>
   </si>
   <si>
-    <t>1245 ms</t>
+    <t>1955 ms</t>
   </si>
   <si>
     <t>testSearchWhenClickingCategoryButton</t>
@@ -74,31 +74,31 @@
     <t>TC_Search_08</t>
   </si>
   <si>
-    <t>1151 ms</t>
+    <t>1148 ms</t>
   </si>
   <si>
     <t>expected [https://totoday.vn/ao-khoac-pc72908.html] but found [https://totoday.vn/]</t>
   </si>
   <si>
-    <t>1137 ms</t>
+    <t>1120 ms</t>
   </si>
   <si>
     <t>expected [https://totoday.vn/do-nam-pc72882.html] but found [https://totoday.vn/]</t>
   </si>
   <si>
-    <t>1160 ms</t>
+    <t>1124 ms</t>
   </si>
   <si>
     <t>expected [https://totoday.vn/do-nu-pc72896.html] but found [https://totoday.vn/]</t>
   </si>
   <si>
-    <t>1182 ms</t>
+    <t>1147 ms</t>
   </si>
   <si>
     <t>expected [https://totoday.vn/unisex-pc72920.html] but found [https://totoday.vn/]</t>
   </si>
   <si>
-    <t>1247 ms</t>
+    <t>1122 ms</t>
   </si>
   <si>
     <t>expected [https://totoday.vn/phu-kien-pc360511.html] but found [https://totoday.vn/]</t>
